--- a/design/Элементы.xlsx
+++ b/design/Элементы.xlsx
@@ -10,13 +10,14 @@
     <sheet name="Атрибуты" sheetId="1" r:id="rId1"/>
     <sheet name="Ресурсы" sheetId="2" r:id="rId2"/>
     <sheet name="Механики" sheetId="3" r:id="rId3"/>
+    <sheet name="Базовые черты" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
   <si>
     <t>Сила</t>
   </si>
@@ -99,9 +100,6 @@
     <t>Дружелюбие?</t>
   </si>
   <si>
-    <t>Характер покемона?</t>
-  </si>
-  <si>
     <t>Атрибут роста имеет в т.ч параметр занимаемой площади</t>
   </si>
   <si>
@@ -192,9 +190,6 @@
     <t>Отвечает за утомление, а также баффы и дебаффы статов покемонов от приемов</t>
   </si>
   <si>
-    <t>Основная для всех прочих тестов. Содержит вторичные механики работы с Приемами покемонов, Умениями и Навыками</t>
-  </si>
-  <si>
     <t>Механики плохих статусов</t>
   </si>
   <si>
@@ -253,6 +248,54 @@
   </si>
   <si>
     <t>НАЗВАНИЕ МЕХАНИК</t>
+  </si>
+  <si>
+    <t>Очередь реализации</t>
+  </si>
+  <si>
+    <t>Название базовой черты</t>
+  </si>
+  <si>
+    <t>Телосложение</t>
+  </si>
+  <si>
+    <t>Масса</t>
+  </si>
+  <si>
+    <t>Тип</t>
+  </si>
+  <si>
+    <t>Черты вида</t>
+  </si>
+  <si>
+    <t>Примечание</t>
+  </si>
+  <si>
+    <t>Различны у каждого вида покемона</t>
+  </si>
+  <si>
+    <t>Характер</t>
+  </si>
+  <si>
+    <t>Механика получения ОД и реакций</t>
+  </si>
+  <si>
+    <t>Механика влияния террейна на юнитов</t>
+  </si>
+  <si>
+    <t>Основная для всех прочих тестов. Содержит вторичные механики работы с Приемами покемонов, Умениями, Чертами, Навыками, Специальностями</t>
+  </si>
+  <si>
+    <t>Механика случайных встреч с покемонами</t>
+  </si>
+  <si>
+    <t>Механика времени суток и года</t>
+  </si>
+  <si>
+    <t>Механика генерации поля для случайных встреч</t>
+  </si>
+  <si>
+    <t>Механика Рационов</t>
   </si>
 </sst>
 </file>
@@ -287,12 +330,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7C80"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -318,7 +367,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -336,6 +385,30 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Заголовок 1" xfId="2" builtinId="16"/>
@@ -344,6 +417,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF7C80"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -639,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -648,7 +726,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>25</v>
@@ -659,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -738,7 +816,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -796,44 +874,39 @@
     </row>
     <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -855,45 +928,45 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -903,177 +976,369 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="10" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="4" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" s="9" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="13" customFormat="1" ht="90.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="8" customFormat="1" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>58</v>
+      <c r="B1" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>68</v>
+      <c r="A3" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/design/Элементы.xlsx
+++ b/design/Элементы.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Атрибуты" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
   <si>
     <t>Сила</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>Механика Рационов</t>
+  </si>
+  <si>
+    <t>Мана</t>
   </si>
 </sst>
 </file>
@@ -382,9 +385,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -408,6 +408,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -736,7 +739,7 @@
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="14" t="s">
         <v>29</v>
       </c>
     </row>
@@ -744,67 +747,67 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6"/>
+      <c r="B3" s="14"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6"/>
+      <c r="B4" s="14"/>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="14"/>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="14"/>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="14"/>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="14"/>
     </row>
     <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="6"/>
+      <c r="B9" s="14"/>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="14"/>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="14"/>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="6"/>
+      <c r="B12" s="14"/>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="14"/>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -919,7 +922,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.28515625" style="1" customWidth="1"/>
@@ -967,6 +970,11 @@
       </c>
       <c r="B8" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -979,314 +987,314 @@
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" style="10" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="19.5703125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="9" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:3" s="8" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="13" customFormat="1" ht="90.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:3" s="12" customFormat="1" ht="90.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="C2" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="90" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="C11" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12">
+      <c r="B12" s="11"/>
+      <c r="C12" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="C18" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="C19" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="C20" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12">
+      <c r="B21" s="11"/>
+      <c r="C21" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="C26" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="B27" s="11"/>
+      <c r="C27" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="B28" s="11"/>
+      <c r="C28" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="B29" s="11"/>
+      <c r="C29" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" s="13" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12">
+      <c r="B32" s="11"/>
+      <c r="C32" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1301,43 +1309,43 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.140625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="8" customFormat="1" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:2" s="7" customFormat="1" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:2" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>85</v>
       </c>
     </row>

--- a/design/Элементы.xlsx
+++ b/design/Элементы.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Атрибуты" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
   <si>
     <t>Сила</t>
   </si>
@@ -299,6 +299,15 @@
   </si>
   <si>
     <t>Мана</t>
+  </si>
+  <si>
+    <t>Механика прокачки</t>
+  </si>
+  <si>
+    <t>Степень успеха</t>
+  </si>
+  <si>
+    <t>результат проверки</t>
   </si>
 </sst>
 </file>
@@ -720,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -910,6 +919,14 @@
       </c>
       <c r="B30" s="1" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -984,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="9" customWidth="1"/>
@@ -1296,6 +1313,11 @@
       <c r="B32" s="11"/>
       <c r="C32" s="11">
         <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
